--- a/main/GeoPolRisk/final_geopolrisk_openlca_colored_verified.xlsx
+++ b/main/GeoPolRisk/final_geopolrisk_openlca_colored_verified.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anish\Nextcloud\Notebook Files\Ecoinvent mapping file\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akoyamparamb\Documents\GitHub\lca-inter-flows\main\GeoPolRisk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CCA3C00A-B986-439E-9BD8-1F34AD5437FE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE33C7B7-352B-4246-92B3-01D493C6BA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="6240" yWindow="4185" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="-1470" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1225" uniqueCount="540">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1226" uniqueCount="541">
   <si>
     <t>ecoinvent Name</t>
   </si>
@@ -1643,6 +1643,9 @@
   </si>
   <si>
     <t>Calcium sulfate</t>
+  </si>
+  <si>
+    <t>Bentonite</t>
   </si>
 </sst>
 </file>
@@ -2301,13 +2304,13 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>122</v>
-      </c>
-      <c r="C8" t="s">
-        <v>237</v>
+        <v>85</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="D8" t="s">
         <v>122</v>
@@ -2316,33 +2319,33 @@
         <v>273</v>
       </c>
       <c r="F8" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="G8" t="s">
-        <v>410</v>
+        <v>373</v>
       </c>
       <c r="H8" t="s">
-        <v>431</v>
+        <v>373</v>
       </c>
       <c r="I8" t="s">
-        <v>526</v>
+        <v>500</v>
       </c>
       <c r="J8" t="s">
         <v>534</v>
       </c>
       <c r="L8" t="s">
-        <v>122</v>
+        <v>85</v>
       </c>
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
       <c r="B9" t="s">
-        <v>85</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>273</v>
+        <v>122</v>
+      </c>
+      <c r="C9" t="s">
+        <v>237</v>
       </c>
       <c r="D9" t="s">
         <v>122</v>
@@ -2351,22 +2354,22 @@
         <v>273</v>
       </c>
       <c r="F9" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="G9" t="s">
-        <v>373</v>
+        <v>410</v>
       </c>
       <c r="H9" t="s">
-        <v>373</v>
+        <v>431</v>
       </c>
       <c r="I9" t="s">
-        <v>500</v>
+        <v>526</v>
       </c>
       <c r="J9" t="s">
         <v>534</v>
       </c>
       <c r="L9" t="s">
-        <v>85</v>
+        <v>122</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
@@ -2715,13 +2718,13 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
       <c r="C20" t="s">
-        <v>54</v>
+        <v>218</v>
       </c>
       <c r="D20" t="s">
         <v>54</v>
@@ -2733,30 +2736,30 @@
         <v>293</v>
       </c>
       <c r="G20" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="H20" t="s">
-        <v>342</v>
+        <v>385</v>
       </c>
       <c r="I20" t="s">
-        <v>477</v>
+        <v>511</v>
       </c>
       <c r="J20" t="s">
         <v>534</v>
       </c>
       <c r="L20" t="s">
-        <v>54</v>
+        <v>97</v>
       </c>
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>218</v>
+        <v>54</v>
       </c>
       <c r="D21" t="s">
         <v>54</v>
@@ -2768,19 +2771,19 @@
         <v>293</v>
       </c>
       <c r="G21" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="H21" t="s">
-        <v>385</v>
+        <v>342</v>
       </c>
       <c r="I21" t="s">
-        <v>511</v>
+        <v>477</v>
       </c>
       <c r="J21" t="s">
         <v>534</v>
       </c>
       <c r="L21" t="s">
-        <v>97</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
@@ -2951,13 +2954,13 @@
     </row>
     <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
       <c r="B27" t="s">
         <v>123</v>
       </c>
       <c r="C27" t="s">
-        <v>253</v>
+        <v>238</v>
       </c>
       <c r="D27" t="s">
         <v>123</v>
@@ -2966,10 +2969,10 @@
         <v>238</v>
       </c>
       <c r="F27" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="G27" t="s">
-        <v>428</v>
+        <v>411</v>
       </c>
       <c r="H27" t="s">
         <v>432</v>
@@ -2981,18 +2984,18 @@
         <v>534</v>
       </c>
       <c r="L27" t="s">
-        <v>140</v>
+        <v>123</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
       <c r="B28" t="s">
         <v>123</v>
       </c>
       <c r="C28" t="s">
-        <v>238</v>
+        <v>253</v>
       </c>
       <c r="D28" t="s">
         <v>123</v>
@@ -3001,10 +3004,10 @@
         <v>238</v>
       </c>
       <c r="F28" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="G28" t="s">
-        <v>411</v>
+        <v>428</v>
       </c>
       <c r="H28" t="s">
         <v>432</v>
@@ -3016,7 +3019,7 @@
         <v>534</v>
       </c>
       <c r="L28" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="29" spans="1:12" x14ac:dyDescent="0.25">
@@ -3359,535 +3362,535 @@
     </row>
     <row r="39" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="B39" t="s">
-        <v>20</v>
+        <v>155</v>
       </c>
       <c r="C39" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="D39" t="s">
         <v>258</v>
       </c>
       <c r="E39" t="s">
-        <v>162</v>
+        <v>255</v>
       </c>
       <c r="F39" t="s">
-        <v>281</v>
+        <v>293</v>
       </c>
       <c r="G39" t="s">
-        <v>308</v>
+        <v>430</v>
       </c>
       <c r="H39" t="s">
-        <v>308</v>
-      </c>
-      <c r="I39" t="s">
-        <v>446</v>
+        <v>430</v>
       </c>
       <c r="J39" t="s">
         <v>534</v>
       </c>
       <c r="L39" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
       <c r="B40" t="s">
-        <v>155</v>
+        <v>100</v>
       </c>
       <c r="C40" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="D40" t="s">
         <v>258</v>
       </c>
       <c r="E40" t="s">
-        <v>255</v>
+        <v>221</v>
       </c>
       <c r="F40" t="s">
-        <v>293</v>
+        <v>278</v>
       </c>
       <c r="G40" t="s">
-        <v>430</v>
+        <v>388</v>
       </c>
       <c r="H40" t="s">
-        <v>430</v>
+        <v>388</v>
+      </c>
+      <c r="I40" t="s">
+        <v>514</v>
       </c>
       <c r="J40" t="s">
         <v>534</v>
       </c>
       <c r="L40" t="s">
-        <v>142</v>
+        <v>100</v>
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>135</v>
+        <v>59</v>
       </c>
       <c r="B41" t="s">
-        <v>152</v>
+        <v>59</v>
       </c>
       <c r="C41" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="D41" t="s">
         <v>258</v>
       </c>
       <c r="E41" t="s">
-        <v>248</v>
+        <v>191</v>
       </c>
       <c r="F41" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G41" t="s">
-        <v>423</v>
+        <v>347</v>
       </c>
       <c r="H41" t="s">
-        <v>423</v>
+        <v>347</v>
+      </c>
+      <c r="I41" t="s">
+        <v>481</v>
       </c>
       <c r="J41" t="s">
         <v>534</v>
-      </c>
-      <c r="L41" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="42" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="B42" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
       <c r="C42" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="D42" t="s">
         <v>258</v>
       </c>
       <c r="E42" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="F42" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="G42" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="H42" t="s">
-        <v>306</v>
+        <v>327</v>
       </c>
       <c r="I42" t="s">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="J42" t="s">
         <v>534</v>
       </c>
       <c r="L42" t="s">
-        <v>18</v>
+        <v>39</v>
       </c>
     </row>
     <row r="43" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="B43" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
       <c r="C43" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="D43" t="s">
         <v>258</v>
       </c>
       <c r="E43" t="s">
-        <v>221</v>
+        <v>160</v>
       </c>
       <c r="F43" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G43" t="s">
-        <v>388</v>
+        <v>306</v>
       </c>
       <c r="H43" t="s">
-        <v>388</v>
+        <v>306</v>
       </c>
       <c r="I43" t="s">
-        <v>514</v>
+        <v>444</v>
       </c>
       <c r="J43" t="s">
         <v>534</v>
       </c>
       <c r="L43" t="s">
-        <v>100</v>
+        <v>18</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="B44" t="s">
-        <v>53</v>
+        <v>37</v>
       </c>
       <c r="C44" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="D44" t="s">
         <v>258</v>
       </c>
       <c r="E44" t="s">
-        <v>188</v>
+        <v>174</v>
       </c>
       <c r="F44" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G44" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="H44" t="s">
-        <v>341</v>
+        <v>325</v>
       </c>
       <c r="I44" t="s">
-        <v>476</v>
+        <v>460</v>
       </c>
       <c r="J44" t="s">
         <v>534</v>
-      </c>
-      <c r="L44" t="s">
-        <v>53</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
       <c r="B45" t="s">
-        <v>35</v>
+        <v>152</v>
       </c>
       <c r="C45" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="D45" t="s">
         <v>258</v>
       </c>
       <c r="E45" t="s">
-        <v>172</v>
+        <v>248</v>
       </c>
       <c r="F45" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="G45" t="s">
-        <v>323</v>
+        <v>423</v>
       </c>
       <c r="H45" t="s">
-        <v>323</v>
-      </c>
-      <c r="I45" t="s">
-        <v>458</v>
+        <v>423</v>
       </c>
       <c r="J45" t="s">
         <v>534</v>
       </c>
       <c r="L45" t="s">
-        <v>35</v>
+        <v>135</v>
       </c>
     </row>
     <row r="46" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
-        <v>129</v>
+        <v>63</v>
       </c>
       <c r="B46" t="s">
-        <v>148</v>
+        <v>63</v>
       </c>
       <c r="C46" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="D46" t="s">
         <v>258</v>
       </c>
       <c r="E46" t="s">
-        <v>243</v>
+        <v>193</v>
       </c>
       <c r="F46" t="s">
-        <v>288</v>
+        <v>275</v>
       </c>
       <c r="G46" t="s">
-        <v>417</v>
+        <v>351</v>
       </c>
       <c r="H46" t="s">
-        <v>417</v>
+        <v>351</v>
+      </c>
+      <c r="I46" t="s">
+        <v>483</v>
       </c>
       <c r="J46" t="s">
         <v>534</v>
-      </c>
-      <c r="L46" t="s">
-        <v>129</v>
       </c>
     </row>
     <row r="47" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>28</v>
+        <v>129</v>
       </c>
       <c r="B47" t="s">
-        <v>28</v>
+        <v>148</v>
       </c>
       <c r="C47" t="s">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="D47" t="s">
         <v>258</v>
       </c>
       <c r="E47" t="s">
-        <v>168</v>
+        <v>243</v>
       </c>
       <c r="F47" t="s">
-        <v>275</v>
+        <v>288</v>
       </c>
       <c r="G47" t="s">
-        <v>316</v>
+        <v>417</v>
       </c>
       <c r="H47" t="s">
-        <v>316</v>
-      </c>
-      <c r="I47" t="s">
-        <v>451</v>
+        <v>417</v>
       </c>
       <c r="J47" t="s">
         <v>534</v>
+      </c>
+      <c r="L47" t="s">
+        <v>129</v>
       </c>
     </row>
     <row r="48" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="B48" t="s">
-        <v>37</v>
+        <v>20</v>
       </c>
       <c r="C48" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="D48" t="s">
         <v>258</v>
       </c>
       <c r="E48" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="F48" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G48" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="H48" t="s">
-        <v>325</v>
+        <v>308</v>
       </c>
       <c r="I48" t="s">
-        <v>460</v>
+        <v>446</v>
       </c>
       <c r="J48" t="s">
         <v>534</v>
+      </c>
+      <c r="L48" t="s">
+        <v>20</v>
       </c>
     </row>
     <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="B49" t="s">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="C49" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="D49" t="s">
         <v>258</v>
       </c>
       <c r="E49" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F49" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="G49" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="H49" t="s">
-        <v>334</v>
+        <v>341</v>
       </c>
       <c r="I49" t="s">
-        <v>469</v>
+        <v>476</v>
       </c>
       <c r="J49" t="s">
         <v>534</v>
+      </c>
+      <c r="L49" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>59</v>
+        <v>119</v>
       </c>
       <c r="B50" t="s">
-        <v>59</v>
+        <v>143</v>
       </c>
       <c r="C50" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="D50" t="s">
         <v>258</v>
       </c>
       <c r="E50" t="s">
-        <v>191</v>
+        <v>234</v>
       </c>
       <c r="F50" t="s">
-        <v>275</v>
+        <v>287</v>
       </c>
       <c r="G50" t="s">
-        <v>347</v>
+        <v>407</v>
       </c>
       <c r="H50" t="s">
-        <v>347</v>
-      </c>
-      <c r="I50" t="s">
-        <v>481</v>
+        <v>407</v>
       </c>
       <c r="J50" t="s">
         <v>534</v>
+      </c>
+      <c r="L50" t="s">
+        <v>119</v>
       </c>
     </row>
     <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="B51" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
       <c r="C51" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="D51" t="s">
         <v>258</v>
       </c>
       <c r="E51" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="F51" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G51" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="H51" t="s">
-        <v>351</v>
+        <v>336</v>
       </c>
       <c r="I51" t="s">
-        <v>483</v>
+        <v>471</v>
       </c>
       <c r="J51" t="s">
         <v>534</v>
+      </c>
+      <c r="L51" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="B52" t="s">
-        <v>39</v>
+        <v>28</v>
       </c>
       <c r="C52" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="D52" t="s">
         <v>258</v>
       </c>
       <c r="E52" t="s">
-        <v>175</v>
+        <v>168</v>
       </c>
       <c r="F52" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G52" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="H52" t="s">
-        <v>327</v>
+        <v>316</v>
       </c>
       <c r="I52" t="s">
-        <v>462</v>
+        <v>451</v>
       </c>
       <c r="J52" t="s">
         <v>534</v>
-      </c>
-      <c r="L52" t="s">
-        <v>39</v>
       </c>
     </row>
     <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B53" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D53" t="s">
         <v>258</v>
       </c>
       <c r="E53" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F53" t="s">
-        <v>292</v>
+        <v>275</v>
       </c>
       <c r="G53" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H53" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="I53" t="s">
-        <v>471</v>
+        <v>469</v>
       </c>
       <c r="J53" t="s">
         <v>534</v>
-      </c>
-      <c r="L53" t="s">
-        <v>48</v>
       </c>
     </row>
     <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
       <c r="B54" t="s">
-        <v>143</v>
+        <v>35</v>
       </c>
       <c r="C54" t="s">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="D54" t="s">
         <v>258</v>
       </c>
       <c r="E54" t="s">
-        <v>234</v>
+        <v>172</v>
       </c>
       <c r="F54" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="G54" t="s">
-        <v>407</v>
+        <v>323</v>
       </c>
       <c r="H54" t="s">
-        <v>407</v>
+        <v>323</v>
+      </c>
+      <c r="I54" t="s">
+        <v>458</v>
       </c>
       <c r="J54" t="s">
         <v>534</v>
       </c>
       <c r="L54" t="s">
-        <v>119</v>
+        <v>35</v>
       </c>
     </row>
     <row r="55" spans="1:12" x14ac:dyDescent="0.25">
@@ -4341,13 +4344,13 @@
     </row>
     <row r="68" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="B68" t="s">
-        <v>64</v>
+        <v>12</v>
       </c>
       <c r="C68" t="s">
-        <v>194</v>
+        <v>156</v>
       </c>
       <c r="D68" t="s">
         <v>64</v>
@@ -4356,33 +4359,30 @@
         <v>194</v>
       </c>
       <c r="F68" t="s">
-        <v>289</v>
+        <v>275</v>
       </c>
       <c r="G68" t="s">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="H68" t="s">
-        <v>352</v>
+        <v>300</v>
       </c>
       <c r="I68" t="s">
-        <v>484</v>
+        <v>439</v>
       </c>
       <c r="J68" t="s">
         <v>534</v>
-      </c>
-      <c r="L68" t="s">
-        <v>64</v>
       </c>
     </row>
     <row r="69" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="B69" t="s">
-        <v>12</v>
+        <v>64</v>
       </c>
       <c r="C69" t="s">
-        <v>156</v>
+        <v>194</v>
       </c>
       <c r="D69" t="s">
         <v>64</v>
@@ -4391,623 +4391,602 @@
         <v>194</v>
       </c>
       <c r="F69" t="s">
-        <v>275</v>
+        <v>289</v>
       </c>
       <c r="G69" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="H69" t="s">
-        <v>300</v>
+        <v>352</v>
       </c>
       <c r="I69" t="s">
-        <v>439</v>
+        <v>484</v>
       </c>
       <c r="J69" t="s">
         <v>534</v>
+      </c>
+      <c r="L69" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="70" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
-        <v>57</v>
+        <v>21</v>
       </c>
       <c r="B70" t="s">
-        <v>57</v>
+        <v>21</v>
+      </c>
+      <c r="C70" t="s">
+        <v>163</v>
       </c>
       <c r="F70" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G70" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="H70" t="s">
-        <v>345</v>
+        <v>309</v>
       </c>
       <c r="I70" t="s">
-        <v>479</v>
+        <v>447</v>
       </c>
       <c r="J70" t="s">
         <v>534</v>
-      </c>
-      <c r="L70" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="71" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
-        <v>137</v>
+        <v>96</v>
       </c>
       <c r="B71" t="s">
-        <v>153</v>
+        <v>96</v>
       </c>
       <c r="C71" t="s">
-        <v>250</v>
+        <v>217</v>
       </c>
       <c r="F71" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
       <c r="G71" t="s">
-        <v>425</v>
+        <v>384</v>
       </c>
       <c r="H71" t="s">
-        <v>425</v>
+        <v>384</v>
+      </c>
+      <c r="I71" t="s">
+        <v>510</v>
       </c>
       <c r="J71" t="s">
         <v>534</v>
-      </c>
-      <c r="L71" t="s">
-        <v>137</v>
       </c>
     </row>
     <row r="72" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
       <c r="B72" t="s">
-        <v>106</v>
-      </c>
-      <c r="C72" t="s">
-        <v>226</v>
+        <v>113</v>
       </c>
       <c r="F72" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="G72" t="s">
-        <v>394</v>
+        <v>401</v>
       </c>
       <c r="H72" t="s">
-        <v>394</v>
-      </c>
-      <c r="I72" t="s">
-        <v>520</v>
+        <v>401</v>
       </c>
       <c r="J72" t="s">
         <v>534</v>
       </c>
       <c r="L72" t="s">
-        <v>106</v>
+        <v>113</v>
       </c>
     </row>
     <row r="73" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="B73" t="s">
-        <v>69</v>
+        <v>56</v>
+      </c>
+      <c r="C73" t="s">
+        <v>189</v>
       </c>
       <c r="F73" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="G73" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="H73" t="s">
-        <v>357</v>
+        <v>344</v>
       </c>
       <c r="I73" t="s">
-        <v>488</v>
+        <v>478</v>
       </c>
       <c r="J73" t="s">
         <v>534</v>
-      </c>
-      <c r="L73" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="74" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
       <c r="B74" t="s">
-        <v>23</v>
+        <v>153</v>
       </c>
       <c r="C74" t="s">
-        <v>164</v>
+        <v>250</v>
       </c>
       <c r="F74" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G74" t="s">
-        <v>311</v>
+        <v>425</v>
       </c>
       <c r="H74" t="s">
-        <v>311</v>
-      </c>
-      <c r="I74" t="s">
-        <v>448</v>
+        <v>425</v>
       </c>
       <c r="J74" t="s">
         <v>534</v>
       </c>
       <c r="L74" t="s">
-        <v>23</v>
+        <v>137</v>
       </c>
     </row>
     <row r="75" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="B75" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
       <c r="C75" t="s">
-        <v>185</v>
+        <v>211</v>
       </c>
       <c r="F75" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="G75" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="H75" t="s">
-        <v>338</v>
+        <v>377</v>
       </c>
       <c r="I75" t="s">
-        <v>473</v>
+        <v>504</v>
       </c>
       <c r="J75" t="s">
         <v>534</v>
       </c>
       <c r="L75" t="s">
-        <v>50</v>
+        <v>89</v>
       </c>
     </row>
     <row r="76" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
-        <v>68</v>
+        <v>62</v>
       </c>
       <c r="B76" t="s">
-        <v>68</v>
+        <v>62</v>
+      </c>
+      <c r="C76" t="s">
+        <v>171</v>
       </c>
       <c r="F76" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="G76" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="H76" t="s">
-        <v>356</v>
+        <v>350</v>
+      </c>
+      <c r="I76" t="s">
+        <v>461</v>
       </c>
       <c r="J76" t="s">
         <v>534</v>
-      </c>
-      <c r="L76" t="s">
-        <v>68</v>
       </c>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="B77" t="s">
-        <v>19</v>
+        <v>38</v>
       </c>
       <c r="C77" t="s">
-        <v>161</v>
+        <v>171</v>
       </c>
       <c r="F77" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G77" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="H77" t="s">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="I77" t="s">
-        <v>445</v>
+        <v>461</v>
       </c>
       <c r="J77" t="s">
         <v>534</v>
-      </c>
-      <c r="L77" t="s">
-        <v>19</v>
       </c>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="B78" t="s">
-        <v>22</v>
+        <v>26</v>
+      </c>
+      <c r="C78" t="s">
+        <v>166</v>
       </c>
       <c r="F78" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="G78" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H78" t="s">
-        <v>310</v>
+        <v>314</v>
+      </c>
+      <c r="I78" t="s">
+        <v>449</v>
       </c>
       <c r="J78" t="s">
         <v>534</v>
       </c>
       <c r="L78" t="s">
-        <v>22</v>
+        <v>26</v>
       </c>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>110</v>
+        <v>58</v>
       </c>
       <c r="B79" t="s">
-        <v>110</v>
+        <v>58</v>
+      </c>
+      <c r="C79" t="s">
+        <v>190</v>
       </c>
       <c r="F79" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="G79" t="s">
-        <v>398</v>
+        <v>346</v>
       </c>
       <c r="H79" t="s">
-        <v>398</v>
+        <v>346</v>
+      </c>
+      <c r="I79" t="s">
+        <v>480</v>
       </c>
       <c r="J79" t="s">
         <v>534</v>
-      </c>
-      <c r="L79" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
       <c r="B80" t="s">
-        <v>109</v>
+        <v>34</v>
+      </c>
+      <c r="D80" t="s">
+        <v>540</v>
       </c>
       <c r="F80" t="s">
-        <v>299</v>
+        <v>283</v>
       </c>
       <c r="G80" t="s">
-        <v>397</v>
+        <v>322</v>
       </c>
       <c r="H80" t="s">
-        <v>397</v>
+        <v>322</v>
+      </c>
+      <c r="I80" t="s">
+        <v>457</v>
       </c>
       <c r="J80" t="s">
         <v>534</v>
       </c>
       <c r="L80" t="s">
-        <v>109</v>
+        <v>34</v>
       </c>
     </row>
     <row r="81" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
       <c r="B81" t="s">
-        <v>117</v>
-      </c>
-      <c r="C81" t="s">
-        <v>232</v>
+        <v>61</v>
       </c>
       <c r="F81" t="s">
-        <v>299</v>
+        <v>294</v>
       </c>
       <c r="G81" t="s">
-        <v>405</v>
+        <v>349</v>
       </c>
       <c r="H81" t="s">
-        <v>405</v>
-      </c>
-      <c r="I81" t="s">
-        <v>525</v>
+        <v>349</v>
       </c>
       <c r="J81" t="s">
         <v>534</v>
       </c>
       <c r="L81" t="s">
-        <v>117</v>
+        <v>61</v>
       </c>
     </row>
     <row r="82" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="B82" t="s">
-        <v>26</v>
+        <v>107</v>
       </c>
       <c r="C82" t="s">
-        <v>166</v>
+        <v>227</v>
       </c>
       <c r="F82" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G82" t="s">
-        <v>314</v>
+        <v>395</v>
       </c>
       <c r="H82" t="s">
-        <v>314</v>
-      </c>
-      <c r="I82" t="s">
-        <v>449</v>
+        <v>395</v>
       </c>
       <c r="J82" t="s">
         <v>534</v>
-      </c>
-      <c r="L82" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="83" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
       <c r="B83" t="s">
-        <v>34</v>
+        <v>23</v>
+      </c>
+      <c r="C83" t="s">
+        <v>164</v>
       </c>
       <c r="F83" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G83" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="H83" t="s">
-        <v>322</v>
+        <v>311</v>
       </c>
       <c r="I83" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="J83" t="s">
         <v>534</v>
       </c>
       <c r="L83" t="s">
-        <v>34</v>
+        <v>23</v>
       </c>
     </row>
     <row r="84" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
-        <v>41</v>
+        <v>80</v>
       </c>
       <c r="B84" t="s">
-        <v>41</v>
-      </c>
-      <c r="C84" t="s">
-        <v>177</v>
+        <v>80</v>
       </c>
       <c r="F84" t="s">
-        <v>283</v>
+        <v>275</v>
       </c>
       <c r="G84" t="s">
-        <v>329</v>
+        <v>368</v>
       </c>
       <c r="H84" t="s">
-        <v>329</v>
-      </c>
-      <c r="I84" t="s">
-        <v>464</v>
+        <v>368</v>
       </c>
       <c r="J84" t="s">
         <v>534</v>
-      </c>
-      <c r="L84" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="85" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
       <c r="B85" t="s">
-        <v>103</v>
+        <v>150</v>
       </c>
       <c r="C85" t="s">
-        <v>223</v>
+        <v>246</v>
       </c>
       <c r="F85" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="G85" t="s">
-        <v>391</v>
+        <v>420</v>
       </c>
       <c r="H85" t="s">
-        <v>391</v>
-      </c>
-      <c r="I85" t="s">
-        <v>517</v>
+        <v>420</v>
       </c>
       <c r="J85" t="s">
         <v>534</v>
       </c>
       <c r="L85" t="s">
-        <v>103</v>
+        <v>132</v>
       </c>
     </row>
     <row r="86" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
       <c r="B86" t="s">
-        <v>151</v>
+        <v>78</v>
+      </c>
+      <c r="C86" t="s">
+        <v>203</v>
       </c>
       <c r="F86" t="s">
-        <v>289</v>
+        <v>285</v>
       </c>
       <c r="G86" t="s">
-        <v>422</v>
+        <v>366</v>
       </c>
       <c r="H86" t="s">
-        <v>422</v>
+        <v>366</v>
+      </c>
+      <c r="I86" t="s">
+        <v>495</v>
       </c>
       <c r="J86" t="s">
         <v>534</v>
       </c>
       <c r="L86" t="s">
-        <v>134</v>
+        <v>78</v>
       </c>
     </row>
     <row r="87" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="B87" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
       <c r="F87" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="G87" t="s">
-        <v>317</v>
+        <v>356</v>
       </c>
       <c r="H87" t="s">
-        <v>317</v>
-      </c>
-      <c r="I87" t="s">
-        <v>452</v>
+        <v>356</v>
       </c>
       <c r="J87" t="s">
         <v>534</v>
       </c>
       <c r="L87" t="s">
-        <v>29</v>
+        <v>68</v>
       </c>
     </row>
     <row r="88" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
-        <v>60</v>
+        <v>75</v>
       </c>
       <c r="B88" t="s">
-        <v>60</v>
-      </c>
-      <c r="C88" t="s">
-        <v>192</v>
+        <v>75</v>
       </c>
       <c r="F88" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="G88" t="s">
-        <v>348</v>
+        <v>363</v>
       </c>
       <c r="H88" t="s">
-        <v>348</v>
-      </c>
-      <c r="I88" t="s">
-        <v>482</v>
+        <v>363</v>
       </c>
       <c r="J88" t="s">
         <v>534</v>
-      </c>
-      <c r="L88" t="s">
-        <v>60</v>
       </c>
     </row>
     <row r="89" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
       <c r="B89" t="s">
-        <v>78</v>
-      </c>
-      <c r="C89" t="s">
-        <v>203</v>
+        <v>151</v>
       </c>
       <c r="F89" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="G89" t="s">
-        <v>366</v>
+        <v>422</v>
       </c>
       <c r="H89" t="s">
-        <v>366</v>
-      </c>
-      <c r="I89" t="s">
-        <v>495</v>
+        <v>422</v>
       </c>
       <c r="J89" t="s">
         <v>534</v>
       </c>
       <c r="L89" t="s">
-        <v>78</v>
+        <v>134</v>
       </c>
     </row>
     <row r="90" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
-        <v>13</v>
+        <v>109</v>
       </c>
       <c r="B90" t="s">
-        <v>13</v>
-      </c>
-      <c r="C90" t="s">
-        <v>157</v>
+        <v>109</v>
       </c>
       <c r="F90" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G90" t="s">
-        <v>301</v>
+        <v>397</v>
       </c>
       <c r="H90" t="s">
-        <v>301</v>
-      </c>
-      <c r="I90" t="s">
-        <v>440</v>
+        <v>397</v>
       </c>
       <c r="J90" t="s">
         <v>534</v>
+      </c>
+      <c r="L90" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="91" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
-        <v>21</v>
+        <v>121</v>
       </c>
       <c r="B91" t="s">
-        <v>21</v>
+        <v>145</v>
       </c>
       <c r="C91" t="s">
-        <v>163</v>
+        <v>236</v>
       </c>
       <c r="F91" t="s">
-        <v>275</v>
+        <v>292</v>
       </c>
       <c r="G91" t="s">
-        <v>309</v>
+        <v>409</v>
       </c>
       <c r="H91" t="s">
-        <v>309</v>
-      </c>
-      <c r="I91" t="s">
-        <v>447</v>
+        <v>409</v>
       </c>
       <c r="J91" t="s">
         <v>534</v>
+      </c>
+      <c r="L91" t="s">
+        <v>121</v>
       </c>
     </row>
     <row r="92" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
-        <v>24</v>
+        <v>91</v>
       </c>
       <c r="B92" t="s">
-        <v>24</v>
+        <v>91</v>
+      </c>
+      <c r="C92" t="s">
+        <v>213</v>
       </c>
       <c r="F92" t="s">
         <v>275</v>
       </c>
       <c r="G92" t="s">
-        <v>312</v>
+        <v>379</v>
       </c>
       <c r="H92" t="s">
-        <v>312</v>
+        <v>379</v>
+      </c>
+      <c r="I92" t="s">
+        <v>506</v>
       </c>
       <c r="J92" t="s">
         <v>534</v>
@@ -5015,515 +4994,515 @@
     </row>
     <row r="93" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="B93" t="s">
-        <v>25</v>
+        <v>103</v>
       </c>
       <c r="C93" t="s">
-        <v>165</v>
+        <v>223</v>
       </c>
       <c r="F93" t="s">
-        <v>275</v>
+        <v>297</v>
       </c>
       <c r="G93" t="s">
-        <v>313</v>
+        <v>391</v>
       </c>
       <c r="H93" t="s">
-        <v>313</v>
+        <v>391</v>
+      </c>
+      <c r="I93" t="s">
+        <v>517</v>
       </c>
       <c r="J93" t="s">
         <v>534</v>
+      </c>
+      <c r="L93" t="s">
+        <v>103</v>
       </c>
     </row>
     <row r="94" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
-        <v>36</v>
-      </c>
-      <c r="B94" t="s">
-        <v>36</v>
+        <v>118</v>
       </c>
       <c r="C94" t="s">
-        <v>173</v>
+        <v>233</v>
       </c>
       <c r="F94" t="s">
         <v>275</v>
       </c>
       <c r="G94" t="s">
-        <v>324</v>
-      </c>
-      <c r="H94" t="s">
-        <v>324</v>
-      </c>
-      <c r="I94" t="s">
-        <v>459</v>
-      </c>
-      <c r="J94" t="s">
-        <v>534</v>
+        <v>406</v>
       </c>
     </row>
     <row r="95" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="B95" t="s">
-        <v>38</v>
+        <v>90</v>
       </c>
       <c r="C95" t="s">
-        <v>171</v>
+        <v>212</v>
       </c>
       <c r="F95" t="s">
-        <v>275</v>
+        <v>295</v>
       </c>
       <c r="G95" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="H95" t="s">
-        <v>326</v>
+        <v>378</v>
       </c>
       <c r="I95" t="s">
-        <v>461</v>
+        <v>505</v>
       </c>
       <c r="J95" t="s">
         <v>534</v>
+      </c>
+      <c r="L95" t="s">
+        <v>90</v>
       </c>
     </row>
     <row r="96" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
-        <v>49</v>
+        <v>22</v>
       </c>
       <c r="B96" t="s">
-        <v>49</v>
-      </c>
-      <c r="C96" t="s">
-        <v>184</v>
+        <v>22</v>
       </c>
       <c r="F96" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G96" t="s">
-        <v>337</v>
+        <v>310</v>
       </c>
       <c r="H96" t="s">
-        <v>337</v>
-      </c>
-      <c r="I96" t="s">
-        <v>472</v>
+        <v>310</v>
       </c>
       <c r="J96" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="97" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L96" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="97" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="B97" t="s">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="F97" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G97" t="s">
-        <v>343</v>
+        <v>302</v>
       </c>
       <c r="H97" t="s">
-        <v>343</v>
+        <v>302</v>
+      </c>
+      <c r="I97" t="s">
+        <v>441</v>
       </c>
       <c r="J97" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="98" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L97" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="98" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
-        <v>56</v>
-      </c>
-      <c r="B98" t="s">
-        <v>56</v>
+        <v>125</v>
       </c>
       <c r="C98" t="s">
-        <v>189</v>
+        <v>240</v>
       </c>
       <c r="F98" t="s">
         <v>275</v>
       </c>
       <c r="G98" t="s">
-        <v>344</v>
-      </c>
-      <c r="H98" t="s">
-        <v>344</v>
-      </c>
-      <c r="I98" t="s">
-        <v>478</v>
-      </c>
-      <c r="J98" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="99" spans="1:10" x14ac:dyDescent="0.25">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="99" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
-        <v>58</v>
+        <v>69</v>
       </c>
       <c r="B99" t="s">
-        <v>58</v>
-      </c>
-      <c r="C99" t="s">
-        <v>190</v>
+        <v>69</v>
       </c>
       <c r="F99" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="G99" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="H99" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="I99" t="s">
-        <v>480</v>
+        <v>488</v>
       </c>
       <c r="J99" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="100" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L99" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="100" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="B100" t="s">
-        <v>62</v>
+        <v>82</v>
       </c>
       <c r="C100" t="s">
-        <v>171</v>
+        <v>205</v>
       </c>
       <c r="F100" t="s">
         <v>275</v>
       </c>
       <c r="G100" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="H100" t="s">
-        <v>350</v>
+        <v>370</v>
       </c>
       <c r="I100" t="s">
-        <v>461</v>
+        <v>497</v>
       </c>
       <c r="J100" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="101" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="B101" t="s">
-        <v>66</v>
+        <v>115</v>
       </c>
       <c r="C101" t="s">
-        <v>196</v>
+        <v>230</v>
       </c>
       <c r="F101" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="G101" t="s">
-        <v>354</v>
+        <v>403</v>
       </c>
       <c r="H101" t="s">
-        <v>354</v>
+        <v>403</v>
       </c>
       <c r="I101" t="s">
-        <v>486</v>
+        <v>523</v>
       </c>
       <c r="J101" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="102" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L101" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="102" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="B102" t="s">
-        <v>67</v>
+        <v>111</v>
       </c>
       <c r="C102" t="s">
-        <v>197</v>
+        <v>228</v>
       </c>
       <c r="F102" t="s">
         <v>275</v>
       </c>
       <c r="G102" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="H102" t="s">
-        <v>355</v>
+        <v>399</v>
       </c>
       <c r="I102" t="s">
-        <v>487</v>
+        <v>521</v>
       </c>
       <c r="J102" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="103" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="B103" t="s">
-        <v>75</v>
+        <v>57</v>
       </c>
       <c r="F103" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="G103" t="s">
-        <v>363</v>
+        <v>345</v>
       </c>
       <c r="H103" t="s">
-        <v>363</v>
+        <v>345</v>
+      </c>
+      <c r="I103" t="s">
+        <v>479</v>
       </c>
       <c r="J103" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="104" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L103" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="104" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
-        <v>80</v>
+        <v>117</v>
       </c>
       <c r="B104" t="s">
-        <v>80</v>
+        <v>117</v>
+      </c>
+      <c r="C104" t="s">
+        <v>232</v>
       </c>
       <c r="F104" t="s">
-        <v>275</v>
+        <v>299</v>
       </c>
       <c r="G104" t="s">
-        <v>368</v>
+        <v>405</v>
       </c>
       <c r="H104" t="s">
-        <v>368</v>
+        <v>405</v>
+      </c>
+      <c r="I104" t="s">
+        <v>525</v>
       </c>
       <c r="J104" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="105" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L104" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="105" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="B105" t="s">
-        <v>82</v>
+        <v>25</v>
       </c>
       <c r="C105" t="s">
-        <v>205</v>
+        <v>165</v>
       </c>
       <c r="F105" t="s">
         <v>275</v>
       </c>
       <c r="G105" t="s">
-        <v>370</v>
+        <v>313</v>
       </c>
       <c r="H105" t="s">
-        <v>370</v>
-      </c>
-      <c r="I105" t="s">
-        <v>497</v>
+        <v>313</v>
       </c>
       <c r="J105" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="106" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="B106" t="s">
-        <v>87</v>
+        <v>98</v>
       </c>
       <c r="C106" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="F106" t="s">
         <v>275</v>
       </c>
       <c r="G106" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="H106" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I106" t="s">
-        <v>502</v>
+        <v>512</v>
       </c>
       <c r="J106" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="107" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="B107" t="s">
-        <v>91</v>
+        <v>106</v>
       </c>
       <c r="C107" t="s">
-        <v>213</v>
+        <v>226</v>
       </c>
       <c r="F107" t="s">
-        <v>275</v>
+        <v>293</v>
       </c>
       <c r="G107" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="H107" t="s">
-        <v>379</v>
+        <v>394</v>
       </c>
       <c r="I107" t="s">
-        <v>506</v>
+        <v>520</v>
       </c>
       <c r="J107" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="108" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L107" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="108" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
-        <v>95</v>
+        <v>67</v>
       </c>
       <c r="B108" t="s">
-        <v>95</v>
+        <v>67</v>
+      </c>
+      <c r="C108" t="s">
+        <v>197</v>
       </c>
       <c r="F108" t="s">
         <v>275</v>
       </c>
       <c r="G108" t="s">
-        <v>383</v>
+        <v>355</v>
       </c>
       <c r="H108" t="s">
-        <v>383</v>
+        <v>355</v>
+      </c>
+      <c r="I108" t="s">
+        <v>487</v>
       </c>
       <c r="J108" t="s">
         <v>534</v>
       </c>
     </row>
-    <row r="109" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>96</v>
-      </c>
-      <c r="B109" t="s">
-        <v>96</v>
+        <v>128</v>
       </c>
       <c r="C109" t="s">
-        <v>217</v>
+        <v>242</v>
       </c>
       <c r="F109" t="s">
         <v>275</v>
       </c>
       <c r="G109" t="s">
-        <v>384</v>
-      </c>
-      <c r="H109" t="s">
-        <v>384</v>
-      </c>
-      <c r="I109" t="s">
-        <v>510</v>
-      </c>
-      <c r="J109" t="s">
-        <v>534</v>
-      </c>
-    </row>
-    <row r="110" spans="1:10" x14ac:dyDescent="0.25">
+        <v>416</v>
+      </c>
+    </row>
+    <row r="110" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>98</v>
+        <v>108</v>
       </c>
       <c r="B110" t="s">
-        <v>98</v>
-      </c>
-      <c r="C110" t="s">
-        <v>219</v>
+        <v>108</v>
       </c>
       <c r="F110" t="s">
-        <v>275</v>
+        <v>294</v>
       </c>
       <c r="G110" t="s">
-        <v>386</v>
+        <v>396</v>
       </c>
       <c r="H110" t="s">
-        <v>386</v>
-      </c>
-      <c r="I110" t="s">
-        <v>512</v>
+        <v>396</v>
       </c>
       <c r="J110" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="111" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L110" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="111" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="B111" t="s">
-        <v>107</v>
-      </c>
-      <c r="C111" t="s">
-        <v>227</v>
+        <v>110</v>
       </c>
       <c r="F111" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G111" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="H111" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="J111" t="s">
         <v>534</v>
       </c>
-    </row>
-    <row r="112" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="L111" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="112" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="B112" t="s">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="C112" t="s">
-        <v>228</v>
+        <v>161</v>
       </c>
       <c r="F112" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="G112" t="s">
-        <v>399</v>
+        <v>307</v>
       </c>
       <c r="H112" t="s">
-        <v>399</v>
+        <v>307</v>
       </c>
       <c r="I112" t="s">
-        <v>521</v>
+        <v>445</v>
       </c>
       <c r="J112" t="s">
         <v>534</v>
+      </c>
+      <c r="L112" t="s">
+        <v>19</v>
       </c>
     </row>
     <row r="113" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="B113" t="s">
-        <v>112</v>
+        <v>87</v>
       </c>
       <c r="C113" t="s">
-        <v>196</v>
+        <v>209</v>
       </c>
       <c r="F113" t="s">
         <v>275</v>
       </c>
       <c r="G113" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="H113" t="s">
-        <v>400</v>
+        <v>375</v>
       </c>
       <c r="I113" t="s">
-        <v>486</v>
+        <v>502</v>
       </c>
       <c r="J113" t="s">
         <v>534</v>
@@ -5531,466 +5510,493 @@
     </row>
     <row r="114" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
-        <v>118</v>
+        <v>27</v>
+      </c>
+      <c r="B114" t="s">
+        <v>27</v>
       </c>
       <c r="C114" t="s">
-        <v>233</v>
+        <v>167</v>
       </c>
       <c r="F114" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="G114" t="s">
-        <v>406</v>
+        <v>315</v>
+      </c>
+      <c r="H114" t="s">
+        <v>315</v>
+      </c>
+      <c r="I114" t="s">
+        <v>450</v>
+      </c>
+      <c r="J114" t="s">
+        <v>534</v>
+      </c>
+      <c r="L114" t="s">
+        <v>27</v>
       </c>
     </row>
     <row r="115" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
-        <v>125</v>
+        <v>141</v>
+      </c>
+      <c r="B115" t="s">
+        <v>154</v>
       </c>
       <c r="C115" t="s">
-        <v>240</v>
+        <v>254</v>
       </c>
       <c r="F115" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="G115" t="s">
-        <v>413</v>
+        <v>429</v>
+      </c>
+      <c r="H115" t="s">
+        <v>429</v>
+      </c>
+      <c r="J115" t="s">
+        <v>534</v>
+      </c>
+      <c r="L115" t="s">
+        <v>141</v>
       </c>
     </row>
     <row r="116" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
-        <v>126</v>
+        <v>105</v>
       </c>
       <c r="B116" t="s">
-        <v>146</v>
+        <v>105</v>
       </c>
       <c r="C116" t="s">
-        <v>241</v>
+        <v>225</v>
       </c>
       <c r="F116" t="s">
-        <v>275</v>
+        <v>298</v>
       </c>
       <c r="G116" t="s">
-        <v>414</v>
+        <v>393</v>
       </c>
       <c r="H116" t="s">
-        <v>414</v>
+        <v>393</v>
+      </c>
+      <c r="I116" t="s">
+        <v>519</v>
       </c>
       <c r="J116" t="s">
         <v>534</v>
+      </c>
+      <c r="L116" t="s">
+        <v>105</v>
       </c>
     </row>
     <row r="117" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
-        <v>128</v>
+        <v>126</v>
+      </c>
+      <c r="B117" t="s">
+        <v>146</v>
       </c>
       <c r="C117" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="F117" t="s">
         <v>275</v>
       </c>
       <c r="G117" t="s">
-        <v>416</v>
+        <v>414</v>
+      </c>
+      <c r="H117" t="s">
+        <v>414</v>
+      </c>
+      <c r="J117" t="s">
+        <v>534</v>
       </c>
     </row>
     <row r="118" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="B118" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
       <c r="C118" t="s">
-        <v>167</v>
+        <v>177</v>
       </c>
       <c r="F118" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G118" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="H118" t="s">
-        <v>315</v>
+        <v>329</v>
       </c>
       <c r="I118" t="s">
-        <v>450</v>
+        <v>464</v>
       </c>
       <c r="J118" t="s">
         <v>534</v>
       </c>
       <c r="L118" t="s">
-        <v>27</v>
+        <v>41</v>
       </c>
     </row>
     <row r="119" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
       <c r="B119" t="s">
-        <v>89</v>
-      </c>
-      <c r="C119" t="s">
-        <v>211</v>
+        <v>102</v>
       </c>
       <c r="F119" t="s">
-        <v>284</v>
+        <v>294</v>
       </c>
       <c r="G119" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="H119" t="s">
-        <v>377</v>
+        <v>390</v>
       </c>
       <c r="I119" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="J119" t="s">
         <v>534</v>
       </c>
       <c r="L119" t="s">
-        <v>89</v>
+        <v>102</v>
       </c>
     </row>
     <row r="120" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
-        <v>141</v>
+        <v>13</v>
       </c>
       <c r="B120" t="s">
-        <v>154</v>
+        <v>13</v>
       </c>
       <c r="C120" t="s">
-        <v>254</v>
+        <v>157</v>
       </c>
       <c r="F120" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G120" t="s">
-        <v>429</v>
+        <v>301</v>
       </c>
       <c r="H120" t="s">
-        <v>429</v>
+        <v>301</v>
+      </c>
+      <c r="I120" t="s">
+        <v>440</v>
       </c>
       <c r="J120" t="s">
         <v>534</v>
-      </c>
-      <c r="L120" t="s">
-        <v>141</v>
       </c>
     </row>
     <row r="121" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
       <c r="B121" t="s">
-        <v>14</v>
+        <v>144</v>
+      </c>
+      <c r="C121" t="s">
+        <v>235</v>
       </c>
       <c r="F121" t="s">
-        <v>276</v>
+        <v>287</v>
       </c>
       <c r="G121" t="s">
-        <v>302</v>
+        <v>408</v>
       </c>
       <c r="H121" t="s">
-        <v>302</v>
-      </c>
-      <c r="I121" t="s">
-        <v>441</v>
+        <v>408</v>
       </c>
       <c r="J121" t="s">
         <v>534</v>
       </c>
       <c r="L121" t="s">
-        <v>14</v>
+        <v>120</v>
       </c>
     </row>
     <row r="122" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="B122" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
       <c r="C122" t="s">
-        <v>230</v>
+        <v>192</v>
       </c>
       <c r="F122" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="G122" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="H122" t="s">
-        <v>403</v>
+        <v>348</v>
       </c>
       <c r="I122" t="s">
-        <v>523</v>
+        <v>482</v>
       </c>
       <c r="J122" t="s">
         <v>534</v>
       </c>
       <c r="L122" t="s">
-        <v>115</v>
+        <v>60</v>
       </c>
     </row>
     <row r="123" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
       <c r="B123" t="s">
-        <v>145</v>
+        <v>50</v>
       </c>
       <c r="C123" t="s">
-        <v>236</v>
+        <v>185</v>
       </c>
       <c r="F123" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="G123" t="s">
-        <v>409</v>
+        <v>338</v>
       </c>
       <c r="H123" t="s">
-        <v>409</v>
+        <v>338</v>
+      </c>
+      <c r="I123" t="s">
+        <v>473</v>
       </c>
       <c r="J123" t="s">
         <v>534</v>
       </c>
       <c r="L123" t="s">
-        <v>121</v>
+        <v>50</v>
       </c>
     </row>
     <row r="124" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="B124" t="s">
-        <v>90</v>
+        <v>36</v>
       </c>
       <c r="C124" t="s">
-        <v>212</v>
+        <v>173</v>
       </c>
       <c r="F124" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G124" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="H124" t="s">
-        <v>378</v>
+        <v>324</v>
       </c>
       <c r="I124" t="s">
-        <v>505</v>
+        <v>459</v>
       </c>
       <c r="J124" t="s">
         <v>534</v>
-      </c>
-      <c r="L124" t="s">
-        <v>90</v>
       </c>
     </row>
     <row r="125" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="B125" t="s">
-        <v>93</v>
+        <v>49</v>
       </c>
       <c r="C125" t="s">
-        <v>215</v>
+        <v>184</v>
       </c>
       <c r="F125" t="s">
-        <v>295</v>
+        <v>275</v>
       </c>
       <c r="G125" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="H125" t="s">
-        <v>381</v>
+        <v>337</v>
       </c>
       <c r="I125" t="s">
-        <v>508</v>
+        <v>472</v>
       </c>
       <c r="J125" t="s">
         <v>534</v>
-      </c>
-      <c r="L125" t="s">
-        <v>93</v>
       </c>
     </row>
     <row r="126" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
       <c r="B126" t="s">
-        <v>61</v>
+        <v>93</v>
+      </c>
+      <c r="C126" t="s">
+        <v>215</v>
       </c>
       <c r="F126" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="G126" t="s">
-        <v>349</v>
+        <v>381</v>
       </c>
       <c r="H126" t="s">
-        <v>349</v>
+        <v>381</v>
+      </c>
+      <c r="I126" t="s">
+        <v>508</v>
       </c>
       <c r="J126" t="s">
         <v>534</v>
       </c>
       <c r="L126" t="s">
-        <v>61</v>
+        <v>93</v>
       </c>
     </row>
     <row r="127" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="B127" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
       <c r="F127" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="G127" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="H127" t="s">
-        <v>390</v>
+        <v>317</v>
       </c>
       <c r="I127" t="s">
-        <v>516</v>
+        <v>452</v>
       </c>
       <c r="J127" t="s">
         <v>534</v>
       </c>
       <c r="L127" t="s">
-        <v>102</v>
+        <v>29</v>
       </c>
     </row>
     <row r="128" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="B128" t="s">
-        <v>108</v>
+        <v>24</v>
       </c>
       <c r="F128" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G128" t="s">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="H128" t="s">
-        <v>396</v>
+        <v>312</v>
       </c>
       <c r="J128" t="s">
         <v>534</v>
       </c>
-      <c r="L128" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="129" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="129" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="B129" t="s">
-        <v>113</v>
+        <v>95</v>
       </c>
       <c r="F129" t="s">
-        <v>294</v>
+        <v>275</v>
       </c>
       <c r="G129" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="H129" t="s">
-        <v>401</v>
+        <v>383</v>
       </c>
       <c r="J129" t="s">
         <v>534</v>
       </c>
-      <c r="L129" t="s">
-        <v>113</v>
-      </c>
-    </row>
-    <row r="130" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="130" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
-        <v>105</v>
+        <v>55</v>
       </c>
       <c r="B130" t="s">
-        <v>105</v>
-      </c>
-      <c r="C130" t="s">
-        <v>225</v>
+        <v>55</v>
       </c>
       <c r="F130" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="G130" t="s">
-        <v>393</v>
+        <v>343</v>
       </c>
       <c r="H130" t="s">
-        <v>393</v>
-      </c>
-      <c r="I130" t="s">
-        <v>519</v>
+        <v>343</v>
       </c>
       <c r="J130" t="s">
         <v>534</v>
       </c>
-      <c r="L130" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="131" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="131" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
-        <v>132</v>
+        <v>112</v>
       </c>
       <c r="B131" t="s">
-        <v>150</v>
+        <v>112</v>
       </c>
       <c r="C131" t="s">
-        <v>246</v>
+        <v>196</v>
       </c>
       <c r="F131" t="s">
-        <v>298</v>
+        <v>275</v>
       </c>
       <c r="G131" t="s">
-        <v>420</v>
+        <v>400</v>
       </c>
       <c r="H131" t="s">
-        <v>420</v>
+        <v>400</v>
+      </c>
+      <c r="I131" t="s">
+        <v>486</v>
       </c>
       <c r="J131" t="s">
         <v>534</v>
       </c>
-      <c r="L131" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="132" spans="1:12" x14ac:dyDescent="0.25">
+    </row>
+    <row r="132" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
-        <v>120</v>
+        <v>66</v>
       </c>
       <c r="B132" t="s">
-        <v>144</v>
+        <v>66</v>
       </c>
       <c r="C132" t="s">
-        <v>235</v>
+        <v>196</v>
       </c>
       <c r="F132" t="s">
-        <v>287</v>
+        <v>275</v>
       </c>
       <c r="G132" t="s">
-        <v>408</v>
+        <v>354</v>
       </c>
       <c r="H132" t="s">
-        <v>408</v>
+        <v>354</v>
+      </c>
+      <c r="I132" t="s">
+        <v>486</v>
       </c>
       <c r="J132" t="s">
         <v>534</v>
-      </c>
-      <c r="L132" t="s">
-        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/main/GeoPolRisk/final_geopolrisk_openlca_colored_verified.xlsx
+++ b/main/GeoPolRisk/final_geopolrisk_openlca_colored_verified.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28925"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\akoyamparamb\Documents\GitHub\lca-inter-flows\main\GeoPolRisk\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CE33C7B7-352B-4246-92B3-01D493C6BA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8F4687F6-0A6E-40B0-BDB3-B7411CE8ACB4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="-1470" windowWidth="14610" windowHeight="17385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1630,9 +1630,6 @@
     <t>Elementary flows/Resource/in ground</t>
   </si>
   <si>
-    <t>Petroleum</t>
-  </si>
-  <si>
     <t>Al(OH)3</t>
   </si>
   <si>
@@ -1646,6 +1643,9 @@
   </si>
   <si>
     <t>Bentonite</t>
+  </si>
+  <si>
+    <t>Crude oil</t>
   </si>
 </sst>
 </file>
@@ -2214,7 +2214,7 @@
         <v>262</v>
       </c>
       <c r="E5" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F5" t="s">
         <v>297</v>
@@ -2695,7 +2695,7 @@
         <v>33</v>
       </c>
       <c r="E19" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="F19" t="s">
         <v>281</v>
@@ -2730,7 +2730,7 @@
         <v>54</v>
       </c>
       <c r="E20" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F20" t="s">
         <v>293</v>
@@ -2765,7 +2765,7 @@
         <v>54</v>
       </c>
       <c r="E21" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="F21" t="s">
         <v>293</v>
@@ -3272,7 +3272,7 @@
         <v>81</v>
       </c>
       <c r="D36" t="s">
-        <v>535</v>
+        <v>540</v>
       </c>
       <c r="E36" t="s">
         <v>271</v>
@@ -4076,7 +4076,7 @@
         <v>16</v>
       </c>
       <c r="E60" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="F60" t="s">
         <v>278</v>
@@ -4680,7 +4680,7 @@
         <v>34</v>
       </c>
       <c r="D80" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="F80" t="s">
         <v>283</v>
